--- a/dev/StructureDefinition-bc-batch-bundle.xlsx
+++ b/dev/StructureDefinition-bc-batch-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T20:38:35+00:00</t>
+    <t>2026-01-23T00:06:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -2135,7 +2135,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>121</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>187</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>191</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>213</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>220</v>
       </c>
@@ -5197,7 +5197,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>226</v>
       </c>
@@ -6779,7 +6779,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>266</v>
       </c>
@@ -7347,7 +7347,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>272</v>
       </c>
@@ -7461,7 +7461,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>273</v>
       </c>
@@ -8255,7 +8255,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>281</v>
       </c>
@@ -8709,7 +8709,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>285</v>
       </c>
@@ -8821,7 +8821,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>286</v>
       </c>
@@ -10521,12 +10521,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN81">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
